--- a/fb_潛客名單_final.xlsx
+++ b/fb_潛客名單_final.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,79 +458,1321 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Wu Zifeng</t>
+          <t>HitYourLung2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/wu.zifeng.9</t>
+          <t>https://www.facebook.com/groups/945818406315161/user/0/</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>juneyao auto</t>
+          <t>個零月之後出優惠價，仲平過一換一税務優惠少少，重要係0首，到時候您咬佢食啊</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/Zhuhaiinsurance/posts/pfbid0XSTnRUi6A6Xtq4P1tUka2mAt3Vfuiq3VeyvpqDSE1HzzbQ6ChLWJD5dPWiEQURjql</t>
+          <t>https://www.facebook.com/groups/945818406315161/permalink/2006837633546561/</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-20 22:52:49</t>
+          <t>2026-04-01 13:15:22</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Wai Leung</t>
+          <t>Bong Lee</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/kawai.leung.79230</t>
+          <t>https://www.facebook.com/groups/945818406315161/user/0/</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>7人油車第三年幾多錢</t>
+          <t>只要佢 31/3 出到車就可以了</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/Zhuhaiinsurance/posts/pfbid0XSTnRUi6A6Xtq4P1tUka2mAt3Vfuiq3VeyvpqDSE1HzzbQ6ChLWJD5dPWiEQURjql</t>
+          <t>https://www.facebook.com/groups/945818406315161/permalink/2006837633546561/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-20 22:52:49</t>
+          <t>2026-04-01 13:15:22</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>David Cheng</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/user/0/</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>加急？掂吾掂架？慢工出細貨~</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/permalink/2006837633546561/</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-04-01 13:15:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Casio</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/user/0/</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>加啦!加多D，快D加到12佰萬1部啦!!都仲有大把人買</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/permalink/2006837633546561/</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-04-01 13:15:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Chun So</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/user/0/</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>個個搶擋車紙個價爆升</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/permalink/2006837633546561/</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-04-01 13:15:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Kam Fat</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/user/0/</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>25/3 前己訂購不受影响，咁25/3 後之後買或者趕尾班車的係咪己經簽咗訂單的轉手新房車？</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/permalink/2006837633546561/</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-04-01 13:15:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sony Ng</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/user/0/</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>剩係睇車價都好似己有升左</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/permalink/2006837633546561/</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-04-01 13:15:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Marion Wong</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/user/0/</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>記得要錄音同叫佢寫明簽名，唔係到時無就車主硬食十幾萬稅。</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/permalink/2006837633546561/</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-04-01 13:15:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HandsomeTulip3963</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/user/0/</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>P靜靜雞咁加咗3萬</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/permalink/2006837633546561/</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-04-01 13:15:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Jason Jason</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/user/0/</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>依家quota 咩走勢</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/permalink/2006837633546561/</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-04-01 13:15:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Anthony Wong</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/user/0/</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>HitYourLung2026 你有無睇過全球定價？ 知唔知星加坡賣幾錢？ 有冇睇過內地而家賣緊幾錢？ 澳門又賣緊幾錢？ 一架車平均利潤唔係好多㗎咋，你覺得一間公司可以減到六成落嚟？ 相反內地品牌電動車就應該做得到啦之後，如果你有返內地去玩嗰時留意個內地嗰啲比亞迪100,000內都有得賣，佢當然大把水位啦，你呢番說話請去返比亞迪嗰邊講。🤣</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/permalink/2006837633546561/</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-04-01 13:15:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Anthony Wong</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/user/61552558451815/</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>HitYourLung2026 你有無睇過全球定價？ 知唔知星加坡賣幾錢？ 有冇睇過內地而家賣緊幾錢？ 澳門又賣緊幾錢？ 一架車平均利潤唔係好多㗎咋，你覺得一間公司可以減到六成落嚟？ 相反內地品牌電動車就應該做得到啦之後，如果你有返內地去玩嗰時留意個內地嗰啲比亞迪100,000內都有得賣，佢當然大把水位啦，你呢番說話請去返比亞迪嗰邊講。🤣</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/permalink/2006837633546561/</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-04-01 13:13:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>HitYourLung2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/user/0/</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>個零月之後出優惠價，仲平過一換一税務優惠少少，重要係0首，到時候您咬佢食啊</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/permalink/2006837633546561/</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-04-01 13:11:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Bong Lee</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/user/0/</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>只要佢 31/3 出到車就可以了</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/permalink/2006837633546561/</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-04-01 13:11:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>David Cheng</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/user/0/</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>加急？掂吾掂架？慢工出細貨~</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/permalink/2006837633546561/</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-04-01 13:11:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Casio</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/user/0/</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>加啦!加多D，快D加到12佰萬1部啦!!都仲有大把人買</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/permalink/2006837633546561/</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-04-01 13:11:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chun So</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/user/0/</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>個個搶擋車紙個價爆升</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/permalink/2006837633546561/</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-04-01 13:11:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Kam Fat</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/user/0/</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>25/3 前己訂購不受影响，咁25/3 後之後買或者趕尾班車的係咪己經簽咗訂單的轉手新房車？</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/permalink/2006837633546561/</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-04-01 13:11:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Sony Ng</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/user/0/</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>剩係睇車價都好似己有升左</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/permalink/2006837633546561/</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-04-01 13:11:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Marion Wong</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/user/0/</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>記得要錄音同叫佢寫明簽名，唔係到時無就車主硬食十幾萬稅。</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/permalink/2006837633546561/</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-04-01 13:11:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>HandsomeTulip3963</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/user/0/</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>P靜靜雞咁加咗3萬</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/permalink/2006837633546561/</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-04-01 13:11:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Jason Jason</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/user/0/</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>依家quota 咩走勢</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/permalink/2006837633546561/</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-04-01 13:11:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>HitYourLung2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/user/0/</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>個零月之後出優惠價，仲平過一換一税務優惠少少，重要係0首，到時候您咬佢食啊</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/permalink/2006837633546561/</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-04-01 13:01:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Bong Lee</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/user/0/</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>只要佢 31/3 出到車就可以了</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/permalink/2006837633546561/</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-04-01 13:01:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>David Cheng</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/user/0/</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>加急？掂吾掂架？慢工出細貨~</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/permalink/2006837633546561/</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-04-01 13:01:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Casio</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/user/0/</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>加啦!加多D，快D加到12佰萬1部啦!!都仲有大把人買</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/permalink/2006837633546561/</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-04-01 13:01:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Chun So</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/user/0/</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>個個搶擋車紙個價爆升</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/permalink/2006837633546561/</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-04-01 13:01:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Kam Fat</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/user/0/</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>25/3 前己訂購不受影响，咁25/3 後之後買或者趕尾班車的係咪己經簽咗訂單的轉手新房車？</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/permalink/2006837633546561/</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-04-01 13:01:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Sony Ng</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/user/0/</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>剩係睇車價都好似己有升左</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/permalink/2006837633546561/</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-04-01 13:01:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Marion Wong</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/user/0/</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>記得要錄音同叫佢寫明簽名，唔係到時無就車主硬食十幾萬稅。</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/permalink/2006837633546561/</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-04-01 13:01:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>HandsomeTulip3963</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/user/0/</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>P靜靜雞咁加咗3萬</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/permalink/2006837633546561/</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-04-01 13:01:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Jason Jason</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/user/0/</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>依家quota 咩走勢</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/permalink/2006837633546561/</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-04-01 13:01:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>HitYourLung2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/user/1555557665525252/</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>個零月之後出優惠價，仲平過一換一税務優惠少少，重要係0首，到時候您咬佢食啊</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/posts/2006837633546561/</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-03-31 12:50:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Bong Lee</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/user/745669606/</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>只要佢 31/3 出到車就可以了</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/posts/2006837633546561/</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-03-31 12:50:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>David Cheng</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/user/525754982/</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>加急？掂吾掂架？慢工出細貨~</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/posts/2006837633546561/</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-03-31 12:50:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Casio</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/user/61584446750614/</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>加啦!加多D，快D加到12佰萬1部啦!!都仲有大把人買</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/posts/2006837633546561/</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-03-31 12:50:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Chun So</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/user/100003168392076/</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>個個搶擋車紙個價爆升</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/posts/2006837633546561/</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-03-31 12:50:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Kam Fat</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/user/100002065805707/</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>25/3 前己訂購不受影响，咁25/3 後之後買或者趕尾班車的係咪己經簽咗訂單的轉手新车？</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/posts/2006837633546561/</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-03-31 12:50:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sony Ng</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/user/806068116/</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>剩係睇車價都好似己有升左</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/posts/2006837633546561/</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026-03-31 12:50:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Marion Wong</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/user/627983217/</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>記得要錄音同叫佢寫明簽名，唔係到時無就車主硬食十幾萬稅。</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/posts/2006837633546561/</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2026-03-31 12:50:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>HandsomeTulip3963</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/user/1595347598364766/</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>P靜靜雞咁加咗3萬</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/posts/2006837633546561/</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2026-03-31 12:50:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Jason Jason</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/user/1841716169/</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>依家quota 咩走勢</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/945818406315161/posts/2006837633546561/</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-03-31 12:50:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>Wwe Hj</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>https://www.facebook.com/wwe.hj.3</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>柴油私家車呢？</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Zhuhaiinsurance/posts/pfbid0XXbp54VohnD2omMsCZTXqeAiazwa9KRUuhodTnq6vpKJUFFrZAobUTAXPGHAFfAvl</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-03-30 17:52:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Wailun Yim</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/wailun.yim.71</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>五人電車怎樣加起來1945？我計到2025 ，有折嗎？</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Zhuhaiinsurance/posts/pfbid0XXbp54VohnD2omMsCZTXqeAiazwa9KRUuhodTnq6vpKJUFFrZAobUTAXPGHAFfAvl</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-03-30 17:52:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Wai Leung</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/kawai.leung.79230</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>7人油車第三年幾多錢</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Zhuhaiinsurance/posts/pfbid0XXbp54VohnD2omMsCZTXqeAiazwa9KRUuhodTnq6vpKJUFFrZAobUTAXPGHAFfAvl</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-03-30 17:52:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Hing Wong</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hing.wong.940</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>續期幾錢？</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Zhuhaiinsurance/posts/pfbid0XXbp54VohnD2omMsCZTXqeAiazwa9KRUuhodTnq6vpKJUFFrZAobUTAXPGHAFfAvl</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-03-30 17:52:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Wu Zifeng</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/wu.zifeng.9</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>juneyao auto</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
         <is>
           <t>https://www.facebook.com/Zhuhaiinsurance/posts/pfbid0XSTnRUi6A6Xtq4P1tUka2mAt3Vfuiq3VeyvpqDSE1HzzbQ6ChLWJD5dPWiEQURjql</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:52:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Wai Leung</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/kawai.leung.79230</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>7人油車第三年幾多錢</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Zhuhaiinsurance/posts/pfbid0XSTnRUi6A6Xtq4P1tUka2mAt3Vfuiq3VeyvpqDSE1HzzbQ6ChLWJD5dPWiEQURjql</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:52:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Wwe Hj</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/wwe.hj.3</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>柴油私家車呢？</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Zhuhaiinsurance/posts/pfbid0XSTnRUi6A6Xtq4P1tUka2mAt3Vfuiq3VeyvpqDSE1HzzbQ6ChLWJD5dPWiEQURjql</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
         <is>
           <t>2026-03-20 22:52:49</t>
         </is>
